--- a/diseases/d125/2010-2014.xlsx
+++ b/diseases/d125/2010-2014.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>13</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>4.086020153508634</v>
       </c>
@@ -1171,9 +1168,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1567,9 +1561,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1963,9 +1954,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2359,9 +2347,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -2755,9 +2740,6 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -3151,9 +3133,6 @@
       <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.06136020855925821</v>
       </c>
@@ -3547,9 +3526,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3943,9 +3919,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4339,9 +4312,6 @@
       <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.04090680570617215</v>
       </c>
@@ -4735,9 +4705,6 @@
       <c r="O22" t="n">
         <v>5</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.1022670142654304</v>
       </c>
@@ -5131,9 +5098,6 @@
       <c r="O24" t="n">
         <v>31</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.6340554884456682</v>
       </c>
@@ -5527,9 +5491,6 @@
       <c r="O26" t="n">
         <v>11</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.2249874313839468</v>
       </c>
@@ -5923,9 +5884,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -6329,9 +6287,6 @@
       <c r="O30" t="n">
         <v>35</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.706647004382019</v>
       </c>
@@ -6725,9 +6680,6 @@
       <c r="O32" t="n">
         <v>33</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.6662671755601894</v>
       </c>
@@ -7121,9 +7073,6 @@
       <c r="O34" t="n">
         <v>31</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.6258873467383598</v>
       </c>
@@ -7517,9 +7466,6 @@
       <c r="O36" t="n">
         <v>31</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.6258873467383598</v>
       </c>
@@ -7913,9 +7859,6 @@
       <c r="O38" t="n">
         <v>34</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.6864570899711042</v>
       </c>
@@ -8309,9 +8252,6 @@
       <c r="O40" t="n">
         <v>45</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.9085461484911672</v>
       </c>
@@ -8705,9 +8645,6 @@
       <c r="O42" t="n">
         <v>24</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.4845579458619559</v>
       </c>
@@ -9101,9 +9038,6 @@
       <c r="O44" t="n">
         <v>17</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.3432285449855521</v>
       </c>
@@ -9497,9 +9431,6 @@
       <c r="O46" t="n">
         <v>16</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.3230386305746373</v>
       </c>
@@ -9893,9 +9824,6 @@
       <c r="O48" t="n">
         <v>8</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.1615193152873186</v>
       </c>
@@ -10289,9 +10217,6 @@
       <c r="O50" t="n">
         <v>14</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2826588017528076</v>
       </c>
@@ -10685,9 +10610,6 @@
       <c r="O52" t="n">
         <v>3</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.06056974323274449</v>
       </c>
@@ -11081,9 +11003,6 @@
       <c r="O54" t="n">
         <v>6</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>1.870088096733424</v>
       </c>
@@ -11726,9 +11645,6 @@
       <c r="O57" t="n">
         <v>13</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.2590437400336658</v>
       </c>
@@ -12361,9 +12277,6 @@
       <c r="O60" t="n">
         <v>18</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.3586759477389218</v>
       </c>
@@ -12996,9 +12909,6 @@
       <c r="O63" t="n">
         <v>14</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.278970181574717</v>
       </c>
@@ -13631,9 +13541,6 @@
       <c r="O66" t="n">
         <v>6</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.1195586492463073</v>
       </c>
@@ -14266,9 +14173,6 @@
       <c r="O69" t="n">
         <v>12</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.2391172984926145</v>
       </c>
@@ -14901,9 +14805,6 @@
       <c r="O72" t="n">
         <v>9</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.1793379738694609</v>
       </c>
@@ -15536,9 +15437,6 @@
       <c r="O75" t="n">
         <v>4</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.07970576616420483</v>
       </c>
@@ -16171,9 +16069,6 @@
       <c r="O78" t="n">
         <v>11</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.2191908569515633</v>
       </c>
@@ -16806,9 +16701,6 @@
       <c r="O81" t="n">
         <v>40</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.7970576616420484</v>
       </c>
@@ -17885,9 +17777,6 @@
       <c r="O87" t="n">
         <v>22</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.4383817139031266</v>
       </c>
@@ -19112,9 +19001,6 @@
       <c r="O94" t="n">
         <v>11</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.2191908569515633</v>
       </c>
@@ -20487,9 +20373,6 @@
       <c r="O102" t="n">
         <v>11</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.2191908569515633</v>
       </c>
@@ -21475,9 +21358,6 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.3087510864178853</v>
       </c>
@@ -22120,9 +22000,6 @@
       <c r="O111" t="n">
         <v>15</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.2952683541515567</v>
       </c>
@@ -23495,9 +23372,6 @@
       <c r="O119" t="n">
         <v>9</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.177161012490934</v>
       </c>
@@ -24722,9 +24596,6 @@
       <c r="O126" t="n">
         <v>8</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.1574764555474969</v>
       </c>
@@ -25949,9 +25820,6 @@
       <c r="O133" t="n">
         <v>17</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.3346374680384309</v>
       </c>
@@ -27176,9 +27044,6 @@
       <c r="O140" t="n">
         <v>8</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.1574764555474969</v>
       </c>
@@ -28551,9 +28416,6 @@
       <c r="O148" t="n">
         <v>9</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.177161012490934</v>
       </c>
@@ -29778,9 +29640,6 @@
       <c r="O155" t="n">
         <v>13</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.2558992402646825</v>
       </c>
@@ -31005,9 +30864,6 @@
       <c r="O162" t="n">
         <v>6</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.1181073416606227</v>
       </c>
@@ -32380,9 +32236,6 @@
       <c r="O170" t="n">
         <v>20</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.3936911388687423</v>
       </c>
@@ -33607,9 +33460,6 @@
       <c r="O177" t="n">
         <v>7</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.1377918986040598</v>
       </c>
@@ -34982,9 +34832,6 @@
       <c r="O185" t="n">
         <v>2</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.03936911388687422</v>
       </c>
@@ -36209,9 +36056,6 @@
       <c r="O192" t="n">
         <v>4</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.07873822777374845</v>
       </c>
@@ -37197,9 +37041,6 @@
       <c r="O198" t="n">
         <v>1</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.3053318575626884</v>
       </c>
@@ -37842,9 +37683,6 @@
       <c r="O201" t="n">
         <v>3</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.05839535406563053</v>
       </c>
@@ -39217,9 +39055,6 @@
       <c r="O209" t="n">
         <v>16</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.3114418883500296</v>
       </c>
@@ -40444,9 +40279,6 @@
       <c r="O216" t="n">
         <v>18</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.3503721243937832</v>
       </c>
@@ -41671,9 +41503,6 @@
       <c r="O223" t="n">
         <v>8</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.1557209441750148</v>
       </c>
@@ -42898,9 +42727,6 @@
       <c r="O230" t="n">
         <v>11</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.2141162982406453</v>
       </c>
@@ -44273,9 +44099,6 @@
       <c r="O238" t="n">
         <v>7</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.1362558261531379</v>
       </c>
@@ -45500,9 +45323,6 @@
       <c r="O245" t="n">
         <v>6</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.1167907081312611</v>
       </c>
@@ -46875,9 +46695,6 @@
       <c r="O253" t="n">
         <v>4</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0.07786047208750739</v>
       </c>
@@ -48102,9 +47919,6 @@
       <c r="O260" t="n">
         <v>7</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.1362558261531379</v>
       </c>
@@ -49329,9 +49143,6 @@
       <c r="O267" t="n">
         <v>6</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.1167907081312611</v>
       </c>
@@ -50704,9 +50515,6 @@
       <c r="O275" t="n">
         <v>17</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.3309070063719064</v>
       </c>
@@ -51930,9 +51738,6 @@
       </c>
       <c r="O282" t="n">
         <v>7</v>
-      </c>
-      <c r="Q282" t="n">
-        <v>0</v>
       </c>
       <c r="R282" t="n">
         <v>0.1362558261531379</v>
